--- a/hourly datasets/cap_gen_year-1final.xlsx
+++ b/hourly datasets/cap_gen_year-1final.xlsx
@@ -485,7 +485,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.1061941420915777</v>
+        <v>0.1017387189438864</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +495,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.07538709310445521</v>
+        <v>0.06853840570769042</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -503,7 +503,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.1815812351960329</v>
+        <v>0.1702771246515768</v>
       </c>
     </row>
     <row r="4">
@@ -513,7 +513,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.09129632098960513</v>
+        <v>0.0751380550387004</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
@@ -521,7 +521,7 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.1974904630811828</v>
+        <v>0.1768767739825868</v>
       </c>
     </row>
     <row r="5">
@@ -531,25 +531,25 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.08244452408814788</v>
+        <v>0.0701548280642309</v>
       </c>
       <c r="C5" t="n">
-        <v>0.009968173993340684</v>
+        <v>0.008226607763422052</v>
       </c>
       <c r="D5" t="n">
-        <v>7.770984081288365</v>
+        <v>-2835604900323.015</v>
       </c>
       <c r="E5" t="n">
-        <v>0.07090955337166575</v>
+        <v>0.07170408105928178</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06289128833426069</v>
+        <v>0.05402627041037101</v>
       </c>
       <c r="G5" t="n">
-        <v>0.1019977598420342</v>
+        <v>0.08628338571809042</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1886386661797255</v>
+        <v>0.1718935470081173</v>
       </c>
     </row>
     <row r="6">
@@ -559,15 +559,25 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.033075347815321</v>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+        <v>0.02661841663851912</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.004671808388524952</v>
+      </c>
+      <c r="D6" t="n">
+        <v>2.679768791098053</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.07989470845479936</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.01745844963960052</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.03577838363743742</v>
+      </c>
       <c r="H6" t="n">
-        <v>0.1392694899068987</v>
+        <v>0.1283571355824055</v>
       </c>
     </row>
     <row r="7">
@@ -577,25 +587,25 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02282775969911425</v>
+        <v>0.01839205292030881</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002877408574986257</v>
+        <v>0.002461333113979741</v>
       </c>
       <c r="D7" t="n">
-        <v>1.413239325310184</v>
+        <v>1.479554908839739</v>
       </c>
       <c r="E7" t="n">
-        <v>0.05824660992423984</v>
+        <v>0.06221229763981839</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01718184450884557</v>
+        <v>0.01356466392410884</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02847367488938306</v>
+        <v>0.02321944191650907</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1290219017906919</v>
+        <v>0.1201307718641952</v>
       </c>
     </row>
     <row r="8">
@@ -605,15 +615,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01432766963596442</v>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
+        <v>0.01117904377100366</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.001461924596837344</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.3224286077022898</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0.05856629007454205</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.008311719716111776</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.01404636782589528</v>
+      </c>
       <c r="H8" t="n">
-        <v>0.1205218117275421</v>
+        <v>0.1129177627148901</v>
       </c>
     </row>
     <row r="9">
@@ -623,25 +643,25 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01128786288893247</v>
+        <v>0.008275068485113909</v>
       </c>
       <c r="C9" t="n">
-        <v>0.006679985189627877</v>
+        <v>0.001422053713111549</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.2362902133199316</v>
+        <v>-0.1548714121066565</v>
       </c>
       <c r="E9" t="n">
-        <v>0.05838131538722428</v>
+        <v>0.03654357069714886</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.00189088772596585</v>
+        <v>0.005486333026532469</v>
       </c>
       <c r="G9" t="n">
-        <v>0.02446661350383084</v>
+        <v>0.01106380394369551</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1174820049805101</v>
+        <v>0.1100137874290003</v>
       </c>
     </row>
     <row r="10">
@@ -651,25 +671,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.005150575418067254</v>
+        <v>0.00270513486691541</v>
       </c>
       <c r="C10" t="n">
-        <v>0.001907382030096153</v>
+        <v>0.0005315659099878724</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.5046112344498452</v>
+        <v>-0.3558380488208547</v>
       </c>
       <c r="E10" t="n">
-        <v>0.04019586879019919</v>
+        <v>0.03673718845706502</v>
       </c>
       <c r="F10" t="n">
-        <v>0.001391177501802804</v>
+        <v>0.001662627909442968</v>
       </c>
       <c r="G10" t="n">
-        <v>0.008909973334331656</v>
+        <v>0.003747641824387895</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1113447175096449</v>
+        <v>0.1044438538108018</v>
       </c>
     </row>
     <row r="11">
@@ -679,7 +699,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.0238976330016012</v>
+        <v>0.02395512021157136</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -687,7 +707,7 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>0.1300917750931788</v>
+        <v>0.1256938391554578</v>
       </c>
     </row>
     <row r="12">
@@ -697,7 +717,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.03790309372304096</v>
+        <v>0.03912346853983614</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -705,7 +725,7 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0.1440972358146186</v>
+        <v>0.1408621874837225</v>
       </c>
     </row>
     <row r="13">
@@ -715,7 +735,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.04458223464389077</v>
+        <v>0.04538328471556196</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -723,7 +743,7 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0.1507763767354684</v>
+        <v>0.1471220036594484</v>
       </c>
     </row>
     <row r="14">
@@ -733,7 +753,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.05086384210138638</v>
+        <v>0.05042273085904952</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
@@ -741,7 +761,7 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0.157057984192964</v>
+        <v>0.1521614498029359</v>
       </c>
     </row>
     <row r="15">
@@ -751,7 +771,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.05543922514084509</v>
+        <v>0.0552822313992261</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -759,7 +779,7 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.1616333672324227</v>
+        <v>0.1570209503431125</v>
       </c>
     </row>
     <row r="16">
@@ -769,25 +789,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.05758888905792175</v>
+        <v>0.05823639247455289</v>
       </c>
       <c r="C16" t="n">
-        <v>0.008283713963978647</v>
+        <v>0.007635322972963763</v>
       </c>
       <c r="D16" t="n">
-        <v>11.85619081500656</v>
+        <v>12.50941866118068</v>
       </c>
       <c r="E16" t="n">
-        <v>0.05071761771923514</v>
+        <v>0.04939663068934536</v>
       </c>
       <c r="F16" t="n">
-        <v>0.04133174130250004</v>
+        <v>0.04325777183466969</v>
       </c>
       <c r="G16" t="n">
-        <v>0.07384603681334358</v>
+        <v>0.07321501311443623</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1637830311494994</v>
+        <v>0.1599751114184393</v>
       </c>
     </row>
     <row r="17">
@@ -797,25 +817,25 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.06246454816749107</v>
+        <v>0.06243470852112248</v>
       </c>
       <c r="C17" t="n">
-        <v>0.008043627690695396</v>
+        <v>0.007431604242963458</v>
       </c>
       <c r="D17" t="n">
-        <v>12.54365822952609</v>
+        <v>12.92039128101153</v>
       </c>
       <c r="E17" t="n">
-        <v>0.04585919853021007</v>
+        <v>0.04678207798648558</v>
       </c>
       <c r="F17" t="n">
-        <v>0.04668213259341834</v>
+        <v>0.04785873768303905</v>
       </c>
       <c r="G17" t="n">
-        <v>0.07824696374156373</v>
+        <v>0.07701067935920582</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1686586902590687</v>
+        <v>0.1641734274650089</v>
       </c>
     </row>
     <row r="18">
@@ -825,22 +845,22 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1061941420915777</v>
+        <v>-0.1017387189438864</v>
       </c>
       <c r="C18" t="n">
-        <v>0.01228733386269351</v>
+        <v>0.0111269788466126</v>
       </c>
       <c r="D18" t="n">
-        <v>-18.60005276615585</v>
+        <v>-17.71022929987314</v>
       </c>
       <c r="E18" t="n">
-        <v>0.03593855487942071</v>
+        <v>0.03819105067997978</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1303675710094518</v>
+        <v>-0.1235618421409401</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.08202071317370364</v>
+        <v>-0.07991559574683287</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
@@ -853,25 +873,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.06571682889121765</v>
+        <v>0.06489038961483942</v>
       </c>
       <c r="C19" t="n">
-        <v>0.0080271893419201</v>
+        <v>0.007393905124507648</v>
       </c>
       <c r="D19" t="n">
-        <v>12.97719454180985</v>
+        <v>2133166559598.27</v>
       </c>
       <c r="E19" t="n">
-        <v>0.05245693064346862</v>
+        <v>0.05123127638590489</v>
       </c>
       <c r="F19" t="n">
-        <v>0.04996430543512473</v>
+        <v>0.05038650893034839</v>
       </c>
       <c r="G19" t="n">
-        <v>0.08146935234731062</v>
+        <v>0.07939427029933049</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1719109709827953</v>
+        <v>0.1666291085587258</v>
       </c>
     </row>
     <row r="20">
@@ -881,25 +901,25 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.06642675937528832</v>
+        <v>0.06502169286544872</v>
       </c>
       <c r="C20" t="n">
-        <v>0.008807015863611984</v>
+        <v>0.007625708468258741</v>
       </c>
       <c r="D20" t="n">
-        <v>12.65377514829668</v>
+        <v>-2072762479785.76</v>
       </c>
       <c r="E20" t="n">
-        <v>0.05440432688346138</v>
+        <v>0.05190796523689804</v>
       </c>
       <c r="F20" t="n">
-        <v>0.04907456038323566</v>
+        <v>0.05006292531010587</v>
       </c>
       <c r="G20" t="n">
-        <v>0.08377895836734112</v>
+        <v>0.07998046042079174</v>
       </c>
       <c r="H20" t="n">
-        <v>0.172620901466866</v>
+        <v>0.1667604118093351</v>
       </c>
     </row>
     <row r="21">
@@ -909,25 +929,25 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.06421143820889143</v>
+        <v>0.06468233774928438</v>
       </c>
       <c r="C21" t="n">
-        <v>0.00850657440918221</v>
+        <v>0.007463610939322558</v>
       </c>
       <c r="D21" t="n">
-        <v>12.43928540507902</v>
+        <v>12.8497600988057</v>
       </c>
       <c r="E21" t="n">
-        <v>0.05047108041171374</v>
+        <v>0.0550077519764037</v>
       </c>
       <c r="F21" t="n">
-        <v>0.04750727662943188</v>
+        <v>0.05004142464393624</v>
       </c>
       <c r="G21" t="n">
-        <v>0.08091559978835082</v>
+        <v>0.07932325085463235</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1704055803004691</v>
+        <v>0.1664210566931708</v>
       </c>
     </row>
     <row r="22">
@@ -937,25 +957,25 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.06771490746122449</v>
+        <v>0.0657760846453625</v>
       </c>
       <c r="C22" t="n">
-        <v>0.008362230008146013</v>
+        <v>0.007589704840343351</v>
       </c>
       <c r="D22" t="n">
-        <v>12.6762303427851</v>
+        <v>12.82768901824398</v>
       </c>
       <c r="E22" t="n">
-        <v>0.05695710903125414</v>
+        <v>0.06003335685888517</v>
       </c>
       <c r="F22" t="n">
-        <v>0.05129907030543083</v>
+        <v>0.05088551078315396</v>
       </c>
       <c r="G22" t="n">
-        <v>0.08413074461701819</v>
+        <v>0.08066665850757126</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1739090495528021</v>
+        <v>0.1675148035892489</v>
       </c>
     </row>
     <row r="23">
@@ -965,25 +985,25 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.0692506945484794</v>
+        <v>0.06770173368137367</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0083450524569745</v>
+        <v>0.007823250466869654</v>
       </c>
       <c r="D23" t="n">
-        <v>13.14085127011487</v>
+        <v>13.19702160869472</v>
       </c>
       <c r="E23" t="n">
-        <v>0.05480444275960535</v>
+        <v>0.05576408018013879</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0528731132637595</v>
+        <v>0.0523551316857602</v>
       </c>
       <c r="G23" t="n">
-        <v>0.08562827583319915</v>
+        <v>0.08304833567698713</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1754448366400571</v>
+        <v>0.1694404526252601</v>
       </c>
     </row>
     <row r="24">
@@ -993,25 +1013,25 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.07152841509902791</v>
+        <v>0.06832488679523667</v>
       </c>
       <c r="C24" t="n">
-        <v>0.00776604083212342</v>
+        <v>0.007603235627602956</v>
       </c>
       <c r="D24" t="n">
-        <v>13.35602331146976</v>
+        <v>13.27109684906578</v>
       </c>
       <c r="E24" t="n">
-        <v>0.05340495578331553</v>
+        <v>0.05868606026875924</v>
       </c>
       <c r="F24" t="n">
-        <v>0.05628916459631818</v>
+        <v>0.05341112650906772</v>
       </c>
       <c r="G24" t="n">
-        <v>0.08676766560173763</v>
+        <v>0.08323864708140571</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1777225571906056</v>
+        <v>0.1700636057391231</v>
       </c>
     </row>
     <row r="25">
@@ -1021,25 +1041,25 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.0716482692395748</v>
+        <v>0.06945328727407617</v>
       </c>
       <c r="C25" t="n">
-        <v>0.00831511932356521</v>
+        <v>0.007842045441141501</v>
       </c>
       <c r="D25" t="n">
-        <v>12.69184647169015</v>
+        <v>12.81023759372188</v>
       </c>
       <c r="E25" t="n">
-        <v>0.06446798172904109</v>
+        <v>0.06927692188125303</v>
       </c>
       <c r="F25" t="n">
-        <v>0.05532522009130807</v>
+        <v>0.05407206271974765</v>
       </c>
       <c r="G25" t="n">
-        <v>0.08797131838784195</v>
+        <v>0.08483451182840483</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1778424113311525</v>
+        <v>0.1711920062179626</v>
       </c>
     </row>
     <row r="26">
@@ -1049,25 +1069,25 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.0735420447311585</v>
+        <v>0.06957644359010036</v>
       </c>
       <c r="C26" t="n">
-        <v>0.008276722301019701</v>
+        <v>0.007896793706498101</v>
       </c>
       <c r="D26" t="n">
-        <v>12.81030019070673</v>
+        <v>12.82982148199321</v>
       </c>
       <c r="E26" t="n">
-        <v>0.05612003391098392</v>
+        <v>0.06691736416366392</v>
       </c>
       <c r="F26" t="n">
-        <v>0.05729873759398849</v>
+        <v>0.05408891164482398</v>
       </c>
       <c r="G26" t="n">
-        <v>0.08978535186832845</v>
+        <v>0.08506397553537677</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1797361868227361</v>
+        <v>0.1713151625339868</v>
       </c>
     </row>
     <row r="27">
@@ -1077,25 +1097,25 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.07390342536206715</v>
+        <v>0.06863732173498906</v>
       </c>
       <c r="C27" t="n">
-        <v>0.009049699157121269</v>
+        <v>0.008124352501652337</v>
       </c>
       <c r="D27" t="n">
-        <v>12.54422792947498</v>
+        <v>-2884196038897.161</v>
       </c>
       <c r="E27" t="n">
-        <v>0.05869854183001363</v>
+        <v>0.05965403338829359</v>
       </c>
       <c r="F27" t="n">
-        <v>0.05613662179409668</v>
+        <v>0.0527036233276867</v>
       </c>
       <c r="G27" t="n">
-        <v>0.09167022893003768</v>
+        <v>0.08457102014229113</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1800975674536448</v>
+        <v>0.1703760406788755</v>
       </c>
     </row>
     <row r="28">
@@ -1105,25 +1125,25 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.0737856038310364</v>
+        <v>0.06921049731632142</v>
       </c>
       <c r="C28" t="n">
-        <v>0.007757768211367496</v>
+        <v>0.007883737756040395</v>
       </c>
       <c r="D28" t="n">
-        <v>12.66078995606631</v>
+        <v>12.67181869674979</v>
       </c>
       <c r="E28" t="n">
-        <v>0.0791336495691254</v>
+        <v>0.08824025557539696</v>
       </c>
       <c r="F28" t="n">
-        <v>0.05856537247682368</v>
+        <v>0.05374785924577487</v>
       </c>
       <c r="G28" t="n">
-        <v>0.08900583518524936</v>
+        <v>0.08467313538686785</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1799797459226141</v>
+        <v>0.1709492162602078</v>
       </c>
     </row>
     <row r="29">
@@ -1133,25 +1153,25 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.02706431340998981</v>
+        <v>0.01172493852594735</v>
       </c>
       <c r="C29" t="n">
-        <v>0.004886929033736671</v>
+        <v>0.001225396942965461</v>
       </c>
       <c r="D29" t="n">
-        <v>0.8147582788376316</v>
+        <v>0.726318150751746</v>
       </c>
       <c r="E29" t="n">
-        <v>0.01181268684215629</v>
+        <v>0.01247246451511542</v>
       </c>
       <c r="F29" t="n">
-        <v>0.01742668874187392</v>
+        <v>0.009318540383360455</v>
       </c>
       <c r="G29" t="n">
-        <v>0.03670193807810559</v>
+        <v>0.01413133666853413</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1332584555015675</v>
+        <v>0.1134636574698338</v>
       </c>
     </row>
   </sheetData>

--- a/hourly datasets/cap_gen_year-1final.xlsx
+++ b/hourly datasets/cap_gen_year-1final.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H29"/>
+  <dimension ref="A1:I29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,6 +466,11 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>first_seen_iter</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>coef_pos</t>
         </is>
       </c>
@@ -477,7 +482,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>0.2306763946087174</v>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
@@ -485,7 +490,10 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
-        <v>0.1017387189438864</v>
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>0.0952725918470988</v>
       </c>
     </row>
     <row r="3">
@@ -495,7 +503,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.06853840570769042</v>
+        <v>0.3308755180079629</v>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr"/>
@@ -503,7 +511,10 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
-        <v>0.1702771246515768</v>
+        <v>2</v>
+      </c>
+      <c r="I3" t="n">
+        <v>0.1954717152463442</v>
       </c>
     </row>
     <row r="4">
@@ -513,7 +524,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0751380550387004</v>
+        <v>0.3273199879479834</v>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
@@ -521,7 +532,10 @@
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
-        <v>0.1768767739825868</v>
+        <v>2</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.1919161851863647</v>
       </c>
     </row>
     <row r="5">
@@ -531,25 +545,28 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0701548280642309</v>
+        <v>0.3449485649647524</v>
       </c>
       <c r="C5" t="n">
-        <v>0.008226607763422052</v>
+        <v>0.01042749959154845</v>
       </c>
       <c r="D5" t="n">
-        <v>-2835604900323.015</v>
+        <v>-2872839170442.24</v>
       </c>
       <c r="E5" t="n">
-        <v>0.07170408105928178</v>
+        <v>0.07369009102521443</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05402627041037101</v>
+        <v>0.06938147811567634</v>
       </c>
       <c r="G5" t="n">
-        <v>0.08628338571809042</v>
+        <v>0.1102672390658321</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1718935470081173</v>
+        <v>4</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0.2095447622031338</v>
       </c>
     </row>
     <row r="6">
@@ -559,25 +576,28 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02661841663851912</v>
+        <v>0.351417978076793</v>
       </c>
       <c r="C6" t="n">
-        <v>0.004671808388524952</v>
+        <v>0.01070477834405589</v>
       </c>
       <c r="D6" t="n">
-        <v>2.679768791098053</v>
+        <v>3.105253084038626</v>
       </c>
       <c r="E6" t="n">
-        <v>0.07989470845479936</v>
+        <v>0.3750791995089182</v>
       </c>
       <c r="F6" t="n">
-        <v>0.01745844963960052</v>
+        <v>0.01833678592692261</v>
       </c>
       <c r="G6" t="n">
-        <v>0.03577838363743742</v>
+        <v>0.06030989768712277</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1283571355824055</v>
+        <v>26</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.2160141753151743</v>
       </c>
     </row>
     <row r="7">
@@ -587,25 +607,28 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.01839205292030881</v>
+        <v>0.4433478928501756</v>
       </c>
       <c r="C7" t="n">
-        <v>0.002461333113979741</v>
+        <v>0.005097977502190437</v>
       </c>
       <c r="D7" t="n">
-        <v>1.479554908839739</v>
+        <v>-0.2207740121349083</v>
       </c>
       <c r="E7" t="n">
-        <v>0.06221229763981839</v>
+        <v>0.4040412451307241</v>
       </c>
       <c r="F7" t="n">
-        <v>0.01356466392410884</v>
+        <v>0.02579784289233946</v>
       </c>
       <c r="G7" t="n">
-        <v>0.02321944191650907</v>
+        <v>0.04579276499720317</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1201307718641952</v>
+        <v>30</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.3079440900885569</v>
       </c>
     </row>
     <row r="8">
@@ -615,25 +638,28 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01117904377100366</v>
+        <v>0.4593753124319042</v>
       </c>
       <c r="C8" t="n">
-        <v>0.001461924596837344</v>
+        <v>0.00376993507050697</v>
       </c>
       <c r="D8" t="n">
-        <v>0.3224286077022898</v>
+        <v>-3.493947162662281</v>
       </c>
       <c r="E8" t="n">
-        <v>0.05856629007454205</v>
+        <v>0.3777874949040964</v>
       </c>
       <c r="F8" t="n">
-        <v>0.008311719716111776</v>
+        <v>0.01895838224591331</v>
       </c>
       <c r="G8" t="n">
-        <v>0.01404636782589528</v>
+        <v>0.03374319251785927</v>
       </c>
       <c r="H8" t="n">
-        <v>0.1129177627148901</v>
+        <v>30</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.3239715096702855</v>
       </c>
     </row>
     <row r="9">
@@ -643,25 +669,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.008275068485113909</v>
+        <v>0.4691141971446826</v>
       </c>
       <c r="C9" t="n">
-        <v>0.001422053713111549</v>
+        <v>0.004579701029476687</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.1548714121066565</v>
+        <v>-4.601892631796284</v>
       </c>
       <c r="E9" t="n">
-        <v>0.03654357069714886</v>
+        <v>0.2420181985388536</v>
       </c>
       <c r="F9" t="n">
-        <v>0.005486333026532469</v>
+        <v>0.01389378741719273</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01106380394369551</v>
+        <v>0.03185165341496086</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1100137874290003</v>
+        <v>30</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.3337103943830639</v>
       </c>
     </row>
     <row r="10">
@@ -671,25 +700,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.00270513486691541</v>
+        <v>0.4908810762756659</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0005315659099878724</v>
+        <v>0.001456495192607211</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.3558380488208547</v>
+        <v>-6.509921776676335</v>
       </c>
       <c r="E10" t="n">
-        <v>0.03673718845706502</v>
+        <v>0.2977506140115334</v>
       </c>
       <c r="F10" t="n">
-        <v>0.001662627909442968</v>
+        <v>-0.004594967605530464</v>
       </c>
       <c r="G10" t="n">
-        <v>0.003747641824387895</v>
+        <v>0.001117013547687547</v>
       </c>
       <c r="H10" t="n">
-        <v>0.1044438538108018</v>
+        <v>30</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.3554772735140472</v>
       </c>
     </row>
     <row r="11">
@@ -699,7 +731,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02395512021157136</v>
+        <v>0.2664292177896014</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
@@ -707,7 +739,10 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
-        <v>0.1256938391554578</v>
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.1310254150279827</v>
       </c>
     </row>
     <row r="12">
@@ -717,7 +752,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.03912346853983614</v>
+        <v>0.2854240131524795</v>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
@@ -725,7 +760,10 @@
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
-        <v>0.1408621874837225</v>
+        <v>1</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.1500202103908609</v>
       </c>
     </row>
     <row r="13">
@@ -735,7 +773,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.04538328471556196</v>
+        <v>0.2935305044213418</v>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
@@ -743,7 +781,10 @@
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
-        <v>0.1471220036594484</v>
+        <v>1</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.1581267016597232</v>
       </c>
     </row>
     <row r="14">
@@ -753,7 +794,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.05042273085904952</v>
+        <v>0.301525481526668</v>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
@@ -761,7 +802,10 @@
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
-        <v>0.1521614498029359</v>
+        <v>1</v>
+      </c>
+      <c r="I14" t="n">
+        <v>0.1661216787650494</v>
       </c>
     </row>
     <row r="15">
@@ -771,7 +815,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.0552822313992261</v>
+        <v>0.3072922491309559</v>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
@@ -779,7 +823,10 @@
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
-        <v>0.1570209503431125</v>
+        <v>1</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0.1718884463693373</v>
       </c>
     </row>
     <row r="16">
@@ -789,25 +836,28 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.05823639247455289</v>
+        <v>0.3113892424037171</v>
       </c>
       <c r="C16" t="n">
-        <v>0.007635322972963763</v>
+        <v>0.007631929761609038</v>
       </c>
       <c r="D16" t="n">
-        <v>12.50941866118068</v>
+        <v>12.50280651789633</v>
       </c>
       <c r="E16" t="n">
-        <v>0.04939663068934536</v>
+        <v>0.04937130653722118</v>
       </c>
       <c r="F16" t="n">
-        <v>0.04325777183466969</v>
+        <v>0.04323493798349422</v>
       </c>
       <c r="G16" t="n">
-        <v>0.07321501311443623</v>
+        <v>0.07317885628609626</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1599751114184393</v>
+        <v>1</v>
+      </c>
+      <c r="I16" t="n">
+        <v>0.1759854396420984</v>
       </c>
     </row>
     <row r="17">
@@ -817,25 +867,28 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.06243470852112248</v>
+        <v>0.3143429996965276</v>
       </c>
       <c r="C17" t="n">
-        <v>0.007431604242963458</v>
+        <v>0.007430089883142756</v>
       </c>
       <c r="D17" t="n">
-        <v>12.92039128101153</v>
+        <v>12.91785607366848</v>
       </c>
       <c r="E17" t="n">
-        <v>0.04678207798648558</v>
+        <v>0.04677051490831045</v>
       </c>
       <c r="F17" t="n">
-        <v>0.04785873768303905</v>
+        <v>0.04784843360343202</v>
       </c>
       <c r="G17" t="n">
-        <v>0.07701067935920582</v>
+        <v>0.07699443305608372</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1641734274650089</v>
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.178939196934909</v>
       </c>
     </row>
     <row r="18">
@@ -845,24 +898,27 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>-0.1017387189438864</v>
+        <v>0.1354038027616186</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0111269788466126</v>
+        <v>0.01108997330266901</v>
       </c>
       <c r="D18" t="n">
-        <v>-17.71022929987314</v>
+        <v>-17.66123680968022</v>
       </c>
       <c r="E18" t="n">
-        <v>0.03819105067997978</v>
+        <v>0.03802813414843628</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1235618421409401</v>
+        <v>-0.123180637092918</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.07991559574683287</v>
+        <v>-0.07967962168485537</v>
       </c>
       <c r="H18" t="n">
+        <v>1</v>
+      </c>
+      <c r="I18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -873,25 +929,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.06489038961483942</v>
+        <v>0.3168767545095091</v>
       </c>
       <c r="C19" t="n">
-        <v>0.007393905124507648</v>
+        <v>0.007391070771787689</v>
       </c>
       <c r="D19" t="n">
-        <v>2133166559598.27</v>
+        <v>2132512005452.91</v>
       </c>
       <c r="E19" t="n">
-        <v>0.05123127638590489</v>
+        <v>0.05120075249235848</v>
       </c>
       <c r="F19" t="n">
-        <v>0.05038650893034839</v>
+        <v>0.0503604418828061</v>
       </c>
       <c r="G19" t="n">
-        <v>0.07939427029933049</v>
+        <v>0.07935707791227266</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1666291085587258</v>
+        <v>1</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.1814729517478904</v>
       </c>
     </row>
     <row r="20">
@@ -901,25 +960,28 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.06502169286544872</v>
+        <v>0.3189832713204065</v>
       </c>
       <c r="C20" t="n">
-        <v>0.007625708468258741</v>
+        <v>0.007636792346846327</v>
       </c>
       <c r="D20" t="n">
-        <v>-2072762479785.76</v>
+        <v>-2075775215948.24</v>
       </c>
       <c r="E20" t="n">
-        <v>0.05190796523689804</v>
+        <v>0.05198341286078888</v>
       </c>
       <c r="F20" t="n">
-        <v>0.05006292531010587</v>
+        <v>0.05013569118991707</v>
       </c>
       <c r="G20" t="n">
-        <v>0.07998046042079174</v>
+        <v>0.080096711090008</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1667604118093351</v>
+        <v>2</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.1835794685587879</v>
       </c>
     </row>
     <row r="21">
@@ -929,25 +991,28 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.06468233774928438</v>
+        <v>0.3177628146920534</v>
       </c>
       <c r="C21" t="n">
-        <v>0.007463610939322558</v>
+        <v>0.00747445921103669</v>
       </c>
       <c r="D21" t="n">
-        <v>12.8497600988057</v>
+        <v>12.8684370756935</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0550077519764037</v>
+        <v>0.05508770510427638</v>
       </c>
       <c r="F21" t="n">
-        <v>0.05004142464393624</v>
+        <v>0.05011415927277917</v>
       </c>
       <c r="G21" t="n">
-        <v>0.07932325085463235</v>
+        <v>0.07943854627738617</v>
       </c>
       <c r="H21" t="n">
-        <v>0.1664210566931708</v>
+        <v>2</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0.1823590119304347</v>
       </c>
     </row>
     <row r="22">
@@ -957,25 +1022,28 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.0657760846453625</v>
+        <v>0.3200062735173633</v>
       </c>
       <c r="C22" t="n">
-        <v>0.007589704840343351</v>
+        <v>0.007600736388076409</v>
       </c>
       <c r="D22" t="n">
-        <v>12.82768901824398</v>
+        <v>12.84633391507282</v>
       </c>
       <c r="E22" t="n">
-        <v>0.06003335685888517</v>
+        <v>0.06012061464501727</v>
       </c>
       <c r="F22" t="n">
-        <v>0.05088551078315396</v>
+        <v>0.05095947228138529</v>
       </c>
       <c r="G22" t="n">
-        <v>0.08066665850757126</v>
+        <v>0.08078390655772762</v>
       </c>
       <c r="H22" t="n">
-        <v>0.1675148035892489</v>
+        <v>2</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.1846024707557447</v>
       </c>
     </row>
     <row r="23">
@@ -985,25 +1053,28 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.06770173368137367</v>
+        <v>0.3239510541868595</v>
       </c>
       <c r="C23" t="n">
-        <v>0.007823250466869654</v>
+        <v>0.007834621470455222</v>
       </c>
       <c r="D23" t="n">
-        <v>13.19702160869472</v>
+        <v>13.21620332614922</v>
       </c>
       <c r="E23" t="n">
-        <v>0.05576408018013879</v>
+        <v>0.05584513262226109</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0523551316857602</v>
+        <v>0.05243122926088484</v>
       </c>
       <c r="G23" t="n">
-        <v>0.08304833567698713</v>
+        <v>0.08316904546721532</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1694404526252601</v>
+        <v>2</v>
+      </c>
+      <c r="I23" t="n">
+        <v>0.1885472514252409</v>
       </c>
     </row>
     <row r="24">
@@ -1013,25 +1084,28 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.06832488679523667</v>
+        <v>0.3244376398853703</v>
       </c>
       <c r="C24" t="n">
-        <v>0.007603235627602956</v>
+        <v>0.007614286842177961</v>
       </c>
       <c r="D24" t="n">
-        <v>13.27109684906578</v>
+        <v>13.29038623402081</v>
       </c>
       <c r="E24" t="n">
-        <v>0.05868606026875924</v>
+        <v>0.05877135977496383</v>
       </c>
       <c r="F24" t="n">
-        <v>0.05341112650906772</v>
+        <v>0.05348875896038904</v>
       </c>
       <c r="G24" t="n">
-        <v>0.08323864708140571</v>
+        <v>0.08335963348704729</v>
       </c>
       <c r="H24" t="n">
-        <v>0.1700636057391231</v>
+        <v>2</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.1890338371237517</v>
       </c>
     </row>
     <row r="25">
@@ -1041,25 +1115,28 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.06945328727407617</v>
+        <v>0.3264715024943438</v>
       </c>
       <c r="C25" t="n">
-        <v>0.007842045441141501</v>
+        <v>0.007853443763003624</v>
       </c>
       <c r="D25" t="n">
-        <v>12.81023759372188</v>
+        <v>12.82885712510811</v>
       </c>
       <c r="E25" t="n">
-        <v>0.06927692188125303</v>
+        <v>0.06937761508166183</v>
       </c>
       <c r="F25" t="n">
-        <v>0.05407206271974765</v>
+        <v>0.0541506558341659</v>
       </c>
       <c r="G25" t="n">
-        <v>0.08483451182840483</v>
+        <v>0.08495781780489961</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1711920062179626</v>
+        <v>2</v>
+      </c>
+      <c r="I25" t="n">
+        <v>0.1910676997327252</v>
       </c>
     </row>
     <row r="26">
@@ -1069,25 +1146,28 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.06957644359010036</v>
+        <v>0.3287952931053142</v>
       </c>
       <c r="C26" t="n">
-        <v>0.007896793706498101</v>
+        <v>0.007908271604327312</v>
       </c>
       <c r="D26" t="n">
-        <v>12.82982148199321</v>
+        <v>12.84846947833331</v>
       </c>
       <c r="E26" t="n">
-        <v>0.06691736416366392</v>
+        <v>0.06701462777436692</v>
       </c>
       <c r="F26" t="n">
-        <v>0.05408891164482398</v>
+        <v>0.05416752924895889</v>
       </c>
       <c r="G26" t="n">
-        <v>0.08506397553537677</v>
+        <v>0.08518761503470144</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1713151625339868</v>
+        <v>2</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0.1933914903436956</v>
       </c>
     </row>
     <row r="27">
@@ -1097,25 +1177,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.06863732173498906</v>
+        <v>0.3291285633720755</v>
       </c>
       <c r="C27" t="n">
-        <v>0.008124352501652337</v>
+        <v>0.008136161153544274</v>
       </c>
       <c r="D27" t="n">
-        <v>-2884196038897.161</v>
+        <v>-2888388184302.535</v>
       </c>
       <c r="E27" t="n">
-        <v>0.05965403338829359</v>
+        <v>0.05974073983217193</v>
       </c>
       <c r="F27" t="n">
-        <v>0.0527036233276867</v>
+        <v>0.05278022743136066</v>
       </c>
       <c r="G27" t="n">
-        <v>0.08457102014229113</v>
+        <v>0.08469394313668401</v>
       </c>
       <c r="H27" t="n">
-        <v>0.1703760406788755</v>
+        <v>2</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0.1937247606104569</v>
       </c>
     </row>
     <row r="28">
@@ -1125,25 +1208,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.06921049731632142</v>
+        <v>0.3301472561184016</v>
       </c>
       <c r="C28" t="n">
-        <v>0.007883737756040395</v>
+        <v>0.00789519667719743</v>
       </c>
       <c r="D28" t="n">
-        <v>12.67181869674979</v>
+        <v>12.69023703787879</v>
       </c>
       <c r="E28" t="n">
-        <v>0.08824025557539696</v>
+        <v>0.08836851176082632</v>
       </c>
       <c r="F28" t="n">
-        <v>0.05374785924577487</v>
+        <v>0.0538259811342135</v>
       </c>
       <c r="G28" t="n">
-        <v>0.08467313538686785</v>
+        <v>0.08479620680458132</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1709492162602078</v>
+        <v>2</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0.1947434533567829</v>
       </c>
     </row>
     <row r="29">
@@ -1153,25 +1239,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.01172493852594735</v>
+        <v>0.4897609011729851</v>
       </c>
       <c r="C29" t="n">
-        <v>0.001225396942965461</v>
+        <v>0.002366098235703022</v>
       </c>
       <c r="D29" t="n">
-        <v>0.726318150751746</v>
+        <v>-17.37600002504656</v>
       </c>
       <c r="E29" t="n">
-        <v>0.01247246451511542</v>
+        <v>0.02247835782235683</v>
       </c>
       <c r="F29" t="n">
-        <v>0.009318540383360455</v>
+        <v>-0.002728896610614236</v>
       </c>
       <c r="G29" t="n">
-        <v>0.01413133666853413</v>
+        <v>0.00655755095930913</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1134636574698338</v>
+        <v>31</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0.3543570984113664</v>
       </c>
     </row>
   </sheetData>
